--- a/reporte_envio.xlsx
+++ b/reporte_envio.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:E17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -407,239 +407,290 @@
         <v>telefono</v>
       </c>
       <c r="C1" t="str">
-        <v>resultado</v>
+        <v>ID</v>
       </c>
       <c r="D1" t="str">
-        <v>fecha_hora</v>
+        <v>resultado_envio</v>
+      </c>
+      <c r="E1" t="str">
+        <v>fecha_procesado</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>hiram</v>
-      </c>
-      <c r="B2">
-        <v>55555</v>
-      </c>
-      <c r="C2" t="str">
-        <v>❌ No tiene WhatsApp</v>
+        <v>puto</v>
+      </c>
+      <c r="B2" t="str">
+        <v>449 497 9850</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
       </c>
       <c r="D2" t="str">
-        <v>26/2/2026, 12:49:18 a.m.</v>
+        <v>✅ Enviado</v>
+      </c>
+      <c r="E2" t="str">
+        <v>5/3/2026, 9:55:39 a.m.</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>i</v>
-      </c>
-      <c r="B3">
-        <v>4492779268</v>
-      </c>
-      <c r="C3" t="str">
-        <v>✅ Enviado</v>
+        <v>puto</v>
+      </c>
+      <c r="B3" t="str">
+        <v>449 497 9850</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
       </c>
       <c r="D3" t="str">
-        <v>26/2/2026, 12:49:24 a.m.</v>
+        <v>✅ Enviado</v>
+      </c>
+      <c r="E3" t="str">
+        <v>5/3/2026, 9:55:43 a.m.</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>j</v>
-      </c>
-      <c r="B4">
-        <v>4492779268</v>
-      </c>
-      <c r="C4" t="str">
-        <v>✅ Enviado</v>
+        <v>puto</v>
+      </c>
+      <c r="B4" t="str">
+        <v>449 497 9850</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
       </c>
       <c r="D4" t="str">
-        <v>26/2/2026, 12:49:30 a.m.</v>
+        <v>✅ Enviado</v>
+      </c>
+      <c r="E4" t="str">
+        <v>5/3/2026, 9:55:47 a.m.</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>k</v>
-      </c>
-      <c r="B5">
-        <v>4492779268</v>
-      </c>
-      <c r="C5" t="str">
-        <v>✅ Enviado</v>
+        <v>puto</v>
+      </c>
+      <c r="B5" t="str">
+        <v>449 497 9850</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
       </c>
       <c r="D5" t="str">
-        <v>26/2/2026, 12:49:35 a.m.</v>
+        <v>✅ Enviado</v>
+      </c>
+      <c r="E5" t="str">
+        <v>5/3/2026, 9:55:52 a.m.</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>montañez</v>
-      </c>
-      <c r="B6">
-        <v>4492779268</v>
-      </c>
-      <c r="C6" t="str">
-        <v>✅ Enviado</v>
+        <v>puto</v>
+      </c>
+      <c r="B6" t="str">
+        <v>449 497 9850</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
       </c>
       <c r="D6" t="str">
-        <v>26/2/2026, 12:49:40 a.m.</v>
+        <v>✅ Enviado</v>
+      </c>
+      <c r="E6" t="str">
+        <v>5/3/2026, 9:55:56 a.m.</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>l</v>
-      </c>
-      <c r="B7">
-        <v>4492779268</v>
-      </c>
-      <c r="C7" t="str">
-        <v>✅ Enviado</v>
+        <v>puto</v>
+      </c>
+      <c r="B7" t="str">
+        <v>449 497 9850</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
       </c>
       <c r="D7" t="str">
-        <v>26/2/2026, 12:49:45 a.m.</v>
+        <v>✅ Enviado</v>
+      </c>
+      <c r="E7" t="str">
+        <v>5/3/2026, 9:56:00 a.m.</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ñ</v>
-      </c>
-      <c r="B8">
-        <v>4492779268</v>
-      </c>
-      <c r="C8" t="str">
-        <v>✅ Enviado</v>
+        <v>puto</v>
+      </c>
+      <c r="B8" t="str">
+        <v>449 497 9850</v>
+      </c>
+      <c r="C8">
+        <v>7</v>
       </c>
       <c r="D8" t="str">
-        <v>26/2/2026, 12:49:51 a.m.</v>
+        <v>✅ Enviado</v>
+      </c>
+      <c r="E8" t="str">
+        <v>5/3/2026, 9:56:05 a.m.</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>o</v>
-      </c>
-      <c r="B9">
-        <v>4492779268</v>
-      </c>
-      <c r="C9" t="str">
-        <v>✅ Enviado</v>
+        <v>puto</v>
+      </c>
+      <c r="B9" t="str">
+        <v>449 497 9850</v>
+      </c>
+      <c r="C9">
+        <v>8</v>
       </c>
       <c r="D9" t="str">
-        <v>26/2/2026, 12:49:58 a.m.</v>
+        <v>✅ Enviado</v>
+      </c>
+      <c r="E9" t="str">
+        <v>5/3/2026, 9:56:08 a.m.</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>p</v>
-      </c>
-      <c r="B10">
-        <v>4492779268</v>
-      </c>
-      <c r="C10" t="str">
-        <v>✅ Enviado</v>
+        <v>puto</v>
+      </c>
+      <c r="B10" t="str">
+        <v>449 497 9850</v>
+      </c>
+      <c r="C10">
+        <v>9</v>
       </c>
       <c r="D10" t="str">
-        <v>26/2/2026, 12:50:03 a.m.</v>
+        <v>✅ Enviado</v>
+      </c>
+      <c r="E10" t="str">
+        <v>5/3/2026, 9:56:12 a.m.</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>q</v>
-      </c>
-      <c r="B11">
-        <v>4492779268</v>
-      </c>
-      <c r="C11" t="str">
-        <v>✅ Enviado</v>
+        <v>puto</v>
+      </c>
+      <c r="B11" t="str">
+        <v>449 497 9850</v>
+      </c>
+      <c r="C11">
+        <v>10</v>
       </c>
       <c r="D11" t="str">
-        <v>26/2/2026, 12:50:10 a.m.</v>
+        <v>✅ Enviado</v>
+      </c>
+      <c r="E11" t="str">
+        <v>5/3/2026, 9:56:16 a.m.</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>r</v>
-      </c>
-      <c r="B12">
-        <v>4492779268</v>
+        <v>puto</v>
+      </c>
+      <c r="B12" t="str">
+        <v>449 497 9850</v>
       </c>
       <c r="C12" t="str">
-        <v>✅ Enviado</v>
+        <v/>
       </c>
       <c r="D12" t="str">
-        <v>26/2/2026, 12:50:17 a.m.</v>
+        <v>✅ Enviado</v>
+      </c>
+      <c r="E12" t="str">
+        <v>5/3/2026, 9:56:22 a.m.</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>s</v>
-      </c>
-      <c r="B13">
-        <v>4492779268</v>
+        <v>puto</v>
+      </c>
+      <c r="B13" t="str">
+        <v>449 497 9850</v>
       </c>
       <c r="C13" t="str">
-        <v>✅ Enviado</v>
+        <v/>
       </c>
       <c r="D13" t="str">
-        <v>26/2/2026, 12:50:22 a.m.</v>
+        <v>✅ Enviado</v>
+      </c>
+      <c r="E13" t="str">
+        <v>5/3/2026, 9:56:26 a.m.</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>t</v>
-      </c>
-      <c r="B14">
-        <v>4492779268</v>
+        <v>puto</v>
+      </c>
+      <c r="B14" t="str">
+        <v>449 497 9850</v>
       </c>
       <c r="C14" t="str">
-        <v>✅ Enviado</v>
+        <v/>
       </c>
       <c r="D14" t="str">
-        <v>26/2/2026, 12:50:27 a.m.</v>
+        <v>✅ Enviado</v>
+      </c>
+      <c r="E14" t="str">
+        <v>5/3/2026, 9:56:30 a.m.</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>u</v>
-      </c>
-      <c r="B15">
-        <v>4492779268</v>
+        <v>puto</v>
+      </c>
+      <c r="B15" t="str">
+        <v>449 497 9850</v>
       </c>
       <c r="C15" t="str">
-        <v>✅ Enviado</v>
+        <v/>
       </c>
       <c r="D15" t="str">
-        <v>26/2/2026, 12:50:34 a.m.</v>
+        <v>✅ Enviado</v>
+      </c>
+      <c r="E15" t="str">
+        <v>5/3/2026, 9:56:34 a.m.</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>v</v>
-      </c>
-      <c r="B16">
-        <v>4492779268</v>
+        <v>puto</v>
+      </c>
+      <c r="B16" t="str">
+        <v>449 497 9850</v>
       </c>
       <c r="C16" t="str">
-        <v>✅ Enviado</v>
+        <v/>
       </c>
       <c r="D16" t="str">
-        <v>26/2/2026, 12:50:38 a.m.</v>
+        <v>✅ Enviado</v>
+      </c>
+      <c r="E16" t="str">
+        <v>5/3/2026, 9:56:41 a.m.</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>w</v>
-      </c>
-      <c r="B17">
-        <v>4492779268</v>
+        <v>puto</v>
+      </c>
+      <c r="B17" t="str">
+        <v>449 497 9850</v>
       </c>
       <c r="C17" t="str">
-        <v>✅ Enviado</v>
+        <v/>
       </c>
       <c r="D17" t="str">
-        <v>26/2/2026, 12:50:44 a.m.</v>
+        <v>✅ Enviado</v>
+      </c>
+      <c r="E17" t="str">
+        <v>5/3/2026, 9:56:44 a.m.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E17"/>
   </ignoredErrors>
 </worksheet>
 </file>